--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_behaviour.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_behaviour.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_behaviour" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="原始动作库" sheetId="6" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_behaviour!$A$1:$U$498</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">cfg_behaviour!$A$4:$V$498</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16901" uniqueCount="1563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16914" uniqueCount="1563">
   <si>
     <t>ID</t>
   </si>
@@ -311,7 +311,7 @@
     <t>所有职业-飞行-空手-安全区待机</t>
   </si>
   <si>
-    <t>21300011#21300021#21300031#21310011#21310021#21310031#21310041#21320011#21320021#21320031#21320041#21320051#21320061#21325011#21325021#21325031#21325041#21325051#21325061#21330011#21330021#21330031#21330041#21330051#21330061#21340011#21340021#21340031#21340041#21340051#21340061#21310501#21310601#21310701#21310801#21310901#21311001#21320501#21320601#21320701#21320801#21320901#21321001#21330501#21330601#21330701#21330801#21330901#21331001#21310501#21310601#21310701#21310801#21310901#21311001#21320501#21320601#21320701#21320801#21320901#21321001#21330501#21330601#21330701#21330801#21330901#21331001#2130001199#2130002199#2130003199#2131001199#2131002199#2131003199#2131004199#2132001199#2132002199#2132003199#2132004199#2132005199#2132006199#2132501199#2132502199#2132503199#2132504199#2132505199#2132506199#2133001199#2133002199#2133003199#2133004199#2133005199#2133006199#2134001199#2134002199#2134003199#2134004199#2134005199#2134006199#2131050199#2131060199#2131070199#2131080199#2131090199#2131100199#2132050199#2132060199#2132070199#2132080199#2132090199#2132100199#2133050199#2133060199#2133070199#2133080199#2133090199#2133100199#2131050199#2131060199#2131070199#2131080199#2131090199#2131100199#2132050199#2132060199#2132070199#2132080199#2132090199#2132100199#2133050199#2133060199#2133070199#2133080199#2133090199#2133100199</t>
+    <t>21300011#21300021#21300031#21310011#21310021#21310031#21310041#21320011#21320021#21320031#21320041#21320051#21320061#21325011#21325021#21325031#21325041#21325051#21330011#21330021#21330031#21330041#21330051#21330061#21340011#21340021#21340031#21340041#21340051#21340061#1554#1555#1556#1557#1573#1574#2130001199#2130002199#2130003199#2131001199#2131002199#2131003199#2131004199#2132001199#2132002199#2132003199#2132004199#2132005199#2132006199#2132501199#2132502199#2132503199#2132504199#2132505199#2133001199#2133002199#2133003199#2133004199#2133005199#2133006199#2134001199#2134002199#2134003199#2134004199#2134005199#2134006199#155499#155599#155699#155799#157399#157499#21325061#2132506199#21370011#21370021#21370031#21370041#2137001199#2137002199#2137003199#2137004199</t>
   </si>
   <si>
     <t>所有职业-飞行-带武器-安全区待机</t>
@@ -4786,7 +4786,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4822,6 +4822,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5341,128 +5347,128 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -5531,17 +5537,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
@@ -5945,11 +5952,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V497"/>
+  <dimension ref="A1:V498"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.875" style="15" customWidth="1"/>
-    <col min="2" max="2" width="30.375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="58.25" style="15" customWidth="1"/>
     <col min="3" max="3" width="9" style="15"/>
     <col min="4" max="4" width="10.5" style="15" customWidth="1"/>
     <col min="5" max="5" width="9" style="15"/>
@@ -6292,7 +6299,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" s="16" customFormat="1" spans="1:22">
+    <row r="6" s="16" customFormat="1" ht="15" spans="1:22">
       <c r="A6" s="16">
         <v>111000001</v>
       </c>
@@ -6314,7 +6321,7 @@
       <c r="H6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K6" s="16" t="s">
@@ -6348,7 +6355,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" s="16" customFormat="1" spans="1:22">
+    <row r="7" s="16" customFormat="1" ht="15" spans="1:22">
       <c r="A7" s="16">
         <v>111000002</v>
       </c>
@@ -6370,7 +6377,7 @@
       <c r="H7" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -6902,7 +6909,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" s="16" customFormat="1" spans="1:21">
+    <row r="17" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A17" s="16">
         <v>112030000</v>
       </c>
@@ -6924,7 +6931,7 @@
       <c r="H17" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K17" s="16" t="s">
@@ -7244,7 +7251,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" s="16" customFormat="1" spans="1:21">
+    <row r="23" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A23" s="16">
         <v>112050000</v>
       </c>
@@ -7266,7 +7273,7 @@
       <c r="H23" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K23" s="16" t="s">
@@ -7300,7 +7307,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" s="16" customFormat="1" spans="1:21">
+    <row r="24" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A24" s="16">
         <v>112050001</v>
       </c>
@@ -7322,7 +7329,7 @@
       <c r="H24" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I24" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K24" s="16" t="s">
@@ -7356,7 +7363,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" s="16" customFormat="1" spans="1:21">
+    <row r="25" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A25" s="16">
         <v>112050002</v>
       </c>
@@ -7378,7 +7385,7 @@
       <c r="H25" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I25" s="16" t="s">
+      <c r="I25" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K25" s="16" t="s">
@@ -7412,7 +7419,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" s="16" customFormat="1" spans="1:21">
+    <row r="26" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A26" s="16">
         <v>112050003</v>
       </c>
@@ -7434,7 +7441,7 @@
       <c r="H26" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="16" t="s">
+      <c r="I26" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K26" s="1" t="s">
@@ -7468,7 +7475,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" s="16" customFormat="1" spans="1:21">
+    <row r="27" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A27" s="16">
         <v>112060000</v>
       </c>
@@ -7490,7 +7497,7 @@
       <c r="H27" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="16" t="s">
+      <c r="I27" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K27" s="16" t="s">
@@ -7524,7 +7531,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" s="16" customFormat="1" spans="1:21">
+    <row r="28" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A28" s="16">
         <v>112060001</v>
       </c>
@@ -7546,7 +7553,7 @@
       <c r="H28" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I28" s="16" t="s">
+      <c r="I28" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K28" s="16" t="s">
@@ -7580,7 +7587,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" s="16" customFormat="1" spans="1:21">
+    <row r="29" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A29" s="16">
         <v>112070000</v>
       </c>
@@ -7602,7 +7609,7 @@
       <c r="H29" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K29" s="16" t="s">
@@ -7636,7 +7643,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" s="16" customFormat="1" spans="1:21">
+    <row r="30" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A30" s="16">
         <v>112070001</v>
       </c>
@@ -7658,7 +7665,7 @@
       <c r="H30" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I30" s="16" t="s">
+      <c r="I30" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J30" s="16">
@@ -7695,7 +7702,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" s="16" customFormat="1" spans="1:21">
+    <row r="31" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A31" s="16">
         <v>112070002</v>
       </c>
@@ -7717,7 +7724,7 @@
       <c r="H31" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I31" s="16" t="s">
+      <c r="I31" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K31" s="16" t="s">
@@ -7751,7 +7758,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" s="16" customFormat="1" spans="1:21">
+    <row r="32" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A32" s="16">
         <v>112070003</v>
       </c>
@@ -7773,7 +7780,7 @@
       <c r="H32" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K32" s="16" t="s">
@@ -7807,7 +7814,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" s="16" customFormat="1" spans="1:21">
+    <row r="33" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A33" s="16">
         <v>112070004</v>
       </c>
@@ -7829,7 +7836,7 @@
       <c r="H33" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I33" s="16" t="s">
+      <c r="I33" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K33" s="16" t="s">
@@ -7863,7 +7870,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" s="16" customFormat="1" spans="1:21">
+    <row r="34" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A34" s="16">
         <v>112070005</v>
       </c>
@@ -7885,7 +7892,7 @@
       <c r="H34" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I34" s="16" t="s">
+      <c r="I34" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K34" s="16" t="s">
@@ -7919,7 +7926,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" s="16" customFormat="1" spans="1:21">
+    <row r="35" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A35" s="16">
         <v>112070006</v>
       </c>
@@ -7941,7 +7948,7 @@
       <c r="H35" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="16" t="s">
+      <c r="I35" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K35" s="1" t="s">
@@ -7975,7 +7982,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" s="16" customFormat="1" spans="1:21">
+    <row r="36" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A36" s="16">
         <v>112070007</v>
       </c>
@@ -7997,7 +8004,7 @@
       <c r="H36" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I36" s="16" t="s">
+      <c r="I36" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J36" s="16">
@@ -8506,7 +8513,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="45" s="17" customFormat="1" spans="1:21">
+    <row r="45" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A45" s="17">
         <v>112230000</v>
       </c>
@@ -8531,7 +8538,7 @@
       <c r="H45" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I45" s="17" t="s">
+      <c r="I45" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K45" s="17" t="s">
@@ -8866,7 +8873,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" s="17" customFormat="1" spans="1:21">
+    <row r="51" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A51" s="17">
         <v>112250000</v>
       </c>
@@ -8891,7 +8898,7 @@
       <c r="H51" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I51" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K51" s="17" t="s">
@@ -8925,7 +8932,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="52" s="17" customFormat="1" spans="1:21">
+    <row r="52" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A52" s="17">
         <v>112250001</v>
       </c>
@@ -8950,7 +8957,7 @@
       <c r="H52" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I52" s="17" t="s">
+      <c r="I52" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K52" s="17" t="s">
@@ -8984,7 +8991,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="53" s="17" customFormat="1" spans="1:21">
+    <row r="53" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A53" s="17">
         <v>112250002</v>
       </c>
@@ -9009,7 +9016,7 @@
       <c r="H53" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I53" s="17" t="s">
+      <c r="I53" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K53" s="17" t="s">
@@ -9043,7 +9050,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" s="17" customFormat="1" spans="1:21">
+    <row r="54" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A54" s="17">
         <v>112250003</v>
       </c>
@@ -9068,7 +9075,7 @@
       <c r="H54" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I54" s="17" t="s">
+      <c r="I54" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K54" s="17" t="s">
@@ -9102,7 +9109,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="55" s="17" customFormat="1" spans="1:21">
+    <row r="55" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A55" s="17">
         <v>112260000</v>
       </c>
@@ -9127,7 +9134,7 @@
       <c r="H55" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I55" s="17" t="s">
+      <c r="I55" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K55" s="17" t="s">
@@ -9161,7 +9168,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="56" s="17" customFormat="1" spans="1:21">
+    <row r="56" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A56" s="17">
         <v>112260001</v>
       </c>
@@ -9186,7 +9193,7 @@
       <c r="H56" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I56" s="17" t="s">
+      <c r="I56" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K56" s="17" t="s">
@@ -9220,7 +9227,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="57" s="17" customFormat="1" spans="1:21">
+    <row r="57" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A57" s="17">
         <v>112270000</v>
       </c>
@@ -9245,7 +9252,7 @@
       <c r="H57" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I57" s="17" t="s">
+      <c r="I57" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K57" s="17" t="s">
@@ -9279,7 +9286,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="58" s="17" customFormat="1" spans="1:21">
+    <row r="58" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A58" s="17">
         <v>112270001</v>
       </c>
@@ -9304,7 +9311,7 @@
       <c r="H58" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I58" s="17" t="s">
+      <c r="I58" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J58" s="17">
@@ -9341,7 +9348,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="59" s="17" customFormat="1" spans="1:21">
+    <row r="59" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A59" s="17">
         <v>112270002</v>
       </c>
@@ -9366,7 +9373,7 @@
       <c r="H59" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I59" s="17" t="s">
+      <c r="I59" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K59" s="17" t="s">
@@ -9400,7 +9407,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="60" s="17" customFormat="1" spans="1:21">
+    <row r="60" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A60" s="17">
         <v>112270003</v>
       </c>
@@ -9425,7 +9432,7 @@
       <c r="H60" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I60" s="17" t="s">
+      <c r="I60" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K60" s="17" t="s">
@@ -9459,7 +9466,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="61" s="17" customFormat="1" spans="1:21">
+    <row r="61" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A61" s="17">
         <v>112270004</v>
       </c>
@@ -9484,7 +9491,7 @@
       <c r="H61" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I61" s="17" t="s">
+      <c r="I61" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K61" s="17" t="s">
@@ -9518,7 +9525,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="62" s="17" customFormat="1" spans="1:21">
+    <row r="62" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A62" s="17">
         <v>112270005</v>
       </c>
@@ -9543,7 +9550,7 @@
       <c r="H62" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I62" s="17" t="s">
+      <c r="I62" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K62" s="17" t="s">
@@ -9577,7 +9584,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="63" s="17" customFormat="1" spans="1:21">
+    <row r="63" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A63" s="17">
         <v>112270006</v>
       </c>
@@ -9602,7 +9609,7 @@
       <c r="H63" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I63" s="17" t="s">
+      <c r="I63" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K63" s="17" t="s">
@@ -9636,7 +9643,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="64" s="17" customFormat="1" spans="1:21">
+    <row r="64" s="17" customFormat="1" ht="15" spans="1:21">
       <c r="A64" s="17">
         <v>112270007</v>
       </c>
@@ -9661,7 +9668,7 @@
       <c r="H64" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I64" s="17" t="s">
+      <c r="I64" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J64" s="17">
@@ -10252,7 +10259,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="75" s="18" customFormat="1" spans="1:21">
+    <row r="75" s="18" customFormat="1" ht="15" spans="1:21">
       <c r="A75" s="18">
         <v>142000008</v>
       </c>
@@ -10274,7 +10281,7 @@
       <c r="H75" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I75" s="18" t="s">
+      <c r="I75" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K75" s="18" t="s">
@@ -10308,7 +10315,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" s="18" customFormat="1" spans="1:21">
+    <row r="76" s="18" customFormat="1" ht="15" spans="1:21">
       <c r="A76" s="18">
         <v>142000009</v>
       </c>
@@ -10330,7 +10337,7 @@
       <c r="H76" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I76" s="18" t="s">
+      <c r="I76" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K76" s="18" t="s">
@@ -10364,7 +10371,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="77" s="18" customFormat="1" spans="1:21">
+    <row r="77" s="18" customFormat="1" ht="15" spans="1:21">
       <c r="A77" s="18">
         <v>142000010</v>
       </c>
@@ -10386,7 +10393,7 @@
       <c r="H77" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I77" s="18" t="s">
+      <c r="I77" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K77" s="18" t="s">
@@ -10420,7 +10427,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="78" s="18" customFormat="1" spans="1:21">
+    <row r="78" s="18" customFormat="1" ht="15" spans="1:21">
       <c r="A78" s="18">
         <v>142000011</v>
       </c>
@@ -10442,7 +10449,7 @@
       <c r="H78" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I78" s="18" t="s">
+      <c r="I78" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K78" s="18" t="s">
@@ -10700,7 +10707,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="83" s="18" customFormat="1" spans="1:21">
+    <row r="83" s="18" customFormat="1" ht="15" spans="1:21">
       <c r="A83" s="18">
         <v>142000016</v>
       </c>
@@ -10722,7 +10729,7 @@
       <c r="H83" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I83" s="18" t="s">
+      <c r="I83" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K83" s="18" t="s">
@@ -10756,7 +10763,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="84" s="18" customFormat="1" spans="1:21">
+    <row r="84" s="18" customFormat="1" ht="15" spans="1:21">
       <c r="A84" s="18">
         <v>142000017</v>
       </c>
@@ -10778,7 +10785,7 @@
       <c r="H84" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I84" s="18" t="s">
+      <c r="I84" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K84" s="18" t="s">
@@ -11279,8 +11286,8 @@
       <c r="E93" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G93" s="16" t="s">
-        <v>72</v>
+      <c r="G93" s="16">
+        <v>0</v>
       </c>
       <c r="H93" s="16" t="s">
         <v>73</v>
@@ -11375,7 +11382,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="95" s="16" customFormat="1" spans="1:21">
+    <row r="95" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A95" s="16">
         <v>212030000</v>
       </c>
@@ -11397,7 +11404,7 @@
       <c r="H95" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I95" s="16" t="s">
+      <c r="I95" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K95" s="16" t="s">
@@ -11937,7 +11944,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="105" s="16" customFormat="1" spans="1:21">
+    <row r="105" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A105" s="16">
         <v>212050000</v>
       </c>
@@ -11959,7 +11966,7 @@
       <c r="H105" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I105" s="16" t="s">
+      <c r="I105" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K105" s="16" t="s">
@@ -11993,7 +12000,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="106" s="16" customFormat="1" spans="1:21">
+    <row r="106" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A106" s="16">
         <v>212050001</v>
       </c>
@@ -12015,7 +12022,7 @@
       <c r="H106" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I106" s="16" t="s">
+      <c r="I106" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K106" s="16" t="s">
@@ -12049,7 +12056,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="107" s="16" customFormat="1" spans="1:21">
+    <row r="107" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A107" s="16">
         <v>212050002</v>
       </c>
@@ -12071,7 +12078,7 @@
       <c r="H107" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I107" s="16" t="s">
+      <c r="I107" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K107" s="16" t="s">
@@ -12105,7 +12112,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="108" s="16" customFormat="1" spans="1:21">
+    <row r="108" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A108" s="16">
         <v>212050003</v>
       </c>
@@ -12127,7 +12134,7 @@
       <c r="H108" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I108" s="16" t="s">
+      <c r="I108" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K108" s="1" t="s">
@@ -12161,7 +12168,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="109" s="16" customFormat="1" spans="1:21">
+    <row r="109" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A109" s="16">
         <v>212060000</v>
       </c>
@@ -12183,7 +12190,7 @@
       <c r="H109" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I109" s="16" t="s">
+      <c r="I109" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K109" s="16" t="s">
@@ -12217,7 +12224,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="110" s="16" customFormat="1" spans="1:21">
+    <row r="110" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A110" s="16">
         <v>212060001</v>
       </c>
@@ -12239,7 +12246,7 @@
       <c r="H110" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I110" s="16" t="s">
+      <c r="I110" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K110" s="16" t="s">
@@ -12273,7 +12280,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="111" s="16" customFormat="1" spans="1:21">
+    <row r="111" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A111" s="16">
         <v>212060002</v>
       </c>
@@ -12295,7 +12302,7 @@
       <c r="H111" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I111" s="16" t="s">
+      <c r="I111" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K111" s="16" t="s">
@@ -12329,7 +12336,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="112" s="16" customFormat="1" spans="1:21">
+    <row r="112" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A112" s="16">
         <v>212070000</v>
       </c>
@@ -12351,7 +12358,7 @@
       <c r="H112" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I112" s="16" t="s">
+      <c r="I112" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K112" s="16" t="s">
@@ -12385,7 +12392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="113" s="16" customFormat="1" spans="1:21">
+    <row r="113" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A113" s="16">
         <v>212070001</v>
       </c>
@@ -12407,7 +12414,7 @@
       <c r="H113" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I113" s="16" t="s">
+      <c r="I113" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J113" s="16">
@@ -12444,7 +12451,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="114" s="16" customFormat="1" spans="1:21">
+    <row r="114" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A114" s="16">
         <v>212070002</v>
       </c>
@@ -12466,7 +12473,7 @@
       <c r="H114" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I114" s="16" t="s">
+      <c r="I114" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K114" s="16" t="s">
@@ -12500,7 +12507,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="115" s="16" customFormat="1" spans="1:21">
+    <row r="115" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A115" s="16">
         <v>212070003</v>
       </c>
@@ -12522,7 +12529,7 @@
       <c r="H115" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I115" s="16" t="s">
+      <c r="I115" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K115" s="16" t="s">
@@ -12556,7 +12563,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="116" s="16" customFormat="1" spans="1:21">
+    <row r="116" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A116" s="16">
         <v>212070004</v>
       </c>
@@ -12578,7 +12585,7 @@
       <c r="H116" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I116" s="16" t="s">
+      <c r="I116" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K116" s="16" t="s">
@@ -12612,7 +12619,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="117" s="16" customFormat="1" spans="1:21">
+    <row r="117" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A117" s="16">
         <v>212070005</v>
       </c>
@@ -12634,7 +12641,7 @@
       <c r="H117" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I117" s="16" t="s">
+      <c r="I117" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K117" s="16" t="s">
@@ -12668,7 +12675,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="118" s="16" customFormat="1" spans="1:21">
+    <row r="118" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A118" s="16">
         <v>212070006</v>
       </c>
@@ -12690,7 +12697,7 @@
       <c r="H118" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I118" s="16" t="s">
+      <c r="I118" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K118" s="16" t="s">
@@ -12724,7 +12731,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="119" s="16" customFormat="1" spans="1:21">
+    <row r="119" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A119" s="16">
         <v>212070007</v>
       </c>
@@ -12746,7 +12753,7 @@
       <c r="H119" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I119" s="16" t="s">
+      <c r="I119" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J119" s="16">
@@ -12783,7 +12790,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="120" s="16" customFormat="1" spans="1:21">
+    <row r="120" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A120" s="16">
         <v>212070008</v>
       </c>
@@ -12805,7 +12812,7 @@
       <c r="H120" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I120" s="16" t="s">
+      <c r="I120" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K120" s="1" t="s">
@@ -13386,7 +13393,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="130" s="16" customFormat="1" spans="1:21">
+    <row r="130" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A130" s="2">
         <v>212230000</v>
       </c>
@@ -13411,7 +13418,7 @@
       <c r="H130" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I130" s="2" t="s">
+      <c r="I130" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J130" s="2"/>
@@ -13978,7 +13985,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="140" s="16" customFormat="1" spans="1:21">
+    <row r="140" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A140" s="16">
         <v>212250000</v>
       </c>
@@ -14003,7 +14010,7 @@
       <c r="H140" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I140" s="16" t="s">
+      <c r="I140" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K140" s="16" t="s">
@@ -14037,7 +14044,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="141" s="16" customFormat="1" spans="1:21">
+    <row r="141" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A141" s="16">
         <v>212250001</v>
       </c>
@@ -14062,7 +14069,7 @@
       <c r="H141" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I141" s="16" t="s">
+      <c r="I141" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K141" s="16" t="s">
@@ -14096,7 +14103,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="142" s="16" customFormat="1" spans="1:21">
+    <row r="142" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A142" s="16">
         <v>212250002</v>
       </c>
@@ -14121,7 +14128,7 @@
       <c r="H142" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I142" s="16" t="s">
+      <c r="I142" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K142" s="16" t="s">
@@ -14152,7 +14159,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="143" s="16" customFormat="1" spans="1:21">
+    <row r="143" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A143" s="16">
         <v>212250003</v>
       </c>
@@ -14177,7 +14184,7 @@
       <c r="H143" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I143" s="16" t="s">
+      <c r="I143" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K143" s="2" t="s">
@@ -14211,7 +14218,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="144" s="16" customFormat="1" spans="1:21">
+    <row r="144" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A144" s="16">
         <v>212260000</v>
       </c>
@@ -14236,7 +14243,7 @@
       <c r="H144" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I144" s="16" t="s">
+      <c r="I144" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K144" s="16" t="s">
@@ -14270,7 +14277,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="145" s="16" customFormat="1" spans="1:21">
+    <row r="145" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A145" s="16">
         <v>212260001</v>
       </c>
@@ -14295,7 +14302,7 @@
       <c r="H145" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I145" s="16" t="s">
+      <c r="I145" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K145" s="16" t="s">
@@ -14329,7 +14336,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="146" s="16" customFormat="1" spans="1:21">
+    <row r="146" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A146" s="16">
         <v>212260002</v>
       </c>
@@ -14354,7 +14361,7 @@
       <c r="H146" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I146" s="16" t="s">
+      <c r="I146" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K146" s="16" t="s">
@@ -14388,7 +14395,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="147" s="16" customFormat="1" spans="1:21">
+    <row r="147" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A147" s="16">
         <v>212270000</v>
       </c>
@@ -14413,7 +14420,7 @@
       <c r="H147" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I147" s="16" t="s">
+      <c r="I147" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K147" s="16" t="s">
@@ -14447,7 +14454,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="148" s="16" customFormat="1" spans="1:21">
+    <row r="148" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A148" s="16">
         <v>212270001</v>
       </c>
@@ -14472,7 +14479,7 @@
       <c r="H148" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I148" s="16" t="s">
+      <c r="I148" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J148" s="2">
@@ -14510,7 +14517,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="149" s="16" customFormat="1" spans="1:21">
+    <row r="149" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A149" s="16">
         <v>212270002</v>
       </c>
@@ -14535,7 +14542,7 @@
       <c r="H149" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I149" s="16" t="s">
+      <c r="I149" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K149" s="16" t="s">
@@ -14569,7 +14576,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="150" s="16" customFormat="1" spans="1:21">
+    <row r="150" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A150" s="16">
         <v>212270003</v>
       </c>
@@ -14594,7 +14601,7 @@
       <c r="H150" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I150" s="16" t="s">
+      <c r="I150" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K150" s="16" t="s">
@@ -14628,7 +14635,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="151" s="16" customFormat="1" spans="1:21">
+    <row r="151" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A151" s="16">
         <v>212270004</v>
       </c>
@@ -14653,7 +14660,7 @@
       <c r="H151" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I151" s="16" t="s">
+      <c r="I151" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K151" s="16" t="s">
@@ -14687,7 +14694,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="152" s="16" customFormat="1" spans="1:21">
+    <row r="152" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A152" s="16">
         <v>212270005</v>
       </c>
@@ -14712,7 +14719,7 @@
       <c r="H152" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I152" s="16" t="s">
+      <c r="I152" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K152" s="16" t="s">
@@ -14746,7 +14753,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="153" s="16" customFormat="1" spans="1:21">
+    <row r="153" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A153" s="16">
         <v>212270006</v>
       </c>
@@ -14771,7 +14778,7 @@
       <c r="H153" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I153" s="16" t="s">
+      <c r="I153" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K153" s="16" t="s">
@@ -14805,7 +14812,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="154" s="16" customFormat="1" spans="1:21">
+    <row r="154" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A154" s="16">
         <v>212270007</v>
       </c>
@@ -14830,7 +14837,7 @@
       <c r="H154" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I154" s="16" t="s">
+      <c r="I154" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J154" s="2">
@@ -14868,7 +14875,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="155" s="16" customFormat="1" spans="1:21">
+    <row r="155" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A155" s="16">
         <v>212270008</v>
       </c>
@@ -14893,7 +14900,7 @@
       <c r="H155" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I155" s="16" t="s">
+      <c r="I155" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K155" s="16" t="s">
@@ -15487,7 +15494,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="166" s="19" customFormat="1" spans="1:21">
+    <row r="166" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A166" s="19">
         <v>222030000</v>
       </c>
@@ -15509,7 +15516,7 @@
       <c r="H166" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I166" s="19" t="s">
+      <c r="I166" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K166" s="19" t="s">
@@ -16049,7 +16056,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="176" s="19" customFormat="1" spans="1:21">
+    <row r="176" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A176" s="19">
         <v>222050000</v>
       </c>
@@ -16071,7 +16078,7 @@
       <c r="H176" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I176" s="19" t="s">
+      <c r="I176" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K176" s="19" t="s">
@@ -16105,7 +16112,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="177" s="19" customFormat="1" spans="1:21">
+    <row r="177" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A177" s="19">
         <v>222050001</v>
       </c>
@@ -16127,7 +16134,7 @@
       <c r="H177" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I177" s="19" t="s">
+      <c r="I177" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K177" s="19" t="s">
@@ -16161,7 +16168,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="178" s="19" customFormat="1" spans="1:21">
+    <row r="178" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A178" s="19">
         <v>222050002</v>
       </c>
@@ -16183,7 +16190,7 @@
       <c r="H178" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I178" s="19" t="s">
+      <c r="I178" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K178" s="19" t="s">
@@ -16217,7 +16224,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="179" s="19" customFormat="1" spans="1:21">
+    <row r="179" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A179" s="19">
         <v>222050003</v>
       </c>
@@ -16239,7 +16246,7 @@
       <c r="H179" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I179" s="19" t="s">
+      <c r="I179" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K179" s="19" t="s">
@@ -16273,7 +16280,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="180" s="19" customFormat="1" spans="1:21">
+    <row r="180" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A180" s="19">
         <v>222060000</v>
       </c>
@@ -16295,7 +16302,7 @@
       <c r="H180" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I180" s="19" t="s">
+      <c r="I180" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K180" s="19" t="s">
@@ -16329,7 +16336,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="181" s="19" customFormat="1" spans="1:21">
+    <row r="181" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A181" s="19">
         <v>222060001</v>
       </c>
@@ -16351,7 +16358,7 @@
       <c r="H181" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I181" s="19" t="s">
+      <c r="I181" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K181" s="19" t="s">
@@ -16385,7 +16392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="182" s="19" customFormat="1" spans="1:21">
+    <row r="182" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A182" s="19">
         <v>222060002</v>
       </c>
@@ -16407,7 +16414,7 @@
       <c r="H182" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I182" s="19" t="s">
+      <c r="I182" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K182" s="19" t="s">
@@ -16441,7 +16448,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="183" s="19" customFormat="1" spans="1:21">
+    <row r="183" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A183" s="19">
         <v>222070000</v>
       </c>
@@ -16463,7 +16470,7 @@
       <c r="H183" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I183" s="19" t="s">
+      <c r="I183" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K183" s="19" t="s">
@@ -16497,7 +16504,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="184" s="19" customFormat="1" spans="1:21">
+    <row r="184" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A184" s="19">
         <v>222070001</v>
       </c>
@@ -16519,7 +16526,7 @@
       <c r="H184" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I184" s="19" t="s">
+      <c r="I184" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J184" s="19">
@@ -16556,7 +16563,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="185" s="19" customFormat="1" spans="1:21">
+    <row r="185" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A185" s="19">
         <v>222070002</v>
       </c>
@@ -16578,7 +16585,7 @@
       <c r="H185" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I185" s="19" t="s">
+      <c r="I185" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K185" s="19" t="s">
@@ -16612,7 +16619,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="186" s="19" customFormat="1" spans="1:21">
+    <row r="186" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A186" s="19">
         <v>222070003</v>
       </c>
@@ -16634,7 +16641,7 @@
       <c r="H186" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I186" s="19" t="s">
+      <c r="I186" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K186" s="19" t="s">
@@ -16668,7 +16675,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="187" s="19" customFormat="1" spans="1:21">
+    <row r="187" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A187" s="19">
         <v>222070004</v>
       </c>
@@ -16690,7 +16697,7 @@
       <c r="H187" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I187" s="19" t="s">
+      <c r="I187" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K187" s="19" t="s">
@@ -16724,7 +16731,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="188" s="19" customFormat="1" spans="1:21">
+    <row r="188" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A188" s="19">
         <v>222070005</v>
       </c>
@@ -16746,7 +16753,7 @@
       <c r="H188" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I188" s="19" t="s">
+      <c r="I188" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K188" s="19" t="s">
@@ -16780,7 +16787,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="189" s="19" customFormat="1" spans="1:21">
+    <row r="189" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A189" s="19">
         <v>222070006</v>
       </c>
@@ -16802,7 +16809,7 @@
       <c r="H189" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I189" s="19" t="s">
+      <c r="I189" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K189" s="19" t="s">
@@ -16836,7 +16843,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="190" s="19" customFormat="1" spans="1:21">
+    <row r="190" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A190" s="19">
         <v>222070007</v>
       </c>
@@ -16858,7 +16865,7 @@
       <c r="H190" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I190" s="19" t="s">
+      <c r="I190" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J190" s="19">
@@ -16895,7 +16902,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="191" s="19" customFormat="1" spans="1:21">
+    <row r="191" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A191" s="19">
         <v>222070008</v>
       </c>
@@ -16917,7 +16924,7 @@
       <c r="H191" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I191" s="19" t="s">
+      <c r="I191" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K191" s="19" t="s">
@@ -17482,7 +17489,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="201" s="19" customFormat="1" spans="1:21">
+    <row r="201" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A201" s="19">
         <v>222230000</v>
       </c>
@@ -17507,7 +17514,7 @@
       <c r="H201" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I201" s="19" t="s">
+      <c r="I201" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K201" s="19" t="s">
@@ -18060,7 +18067,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="211" s="19" customFormat="1" spans="1:21">
+    <row r="211" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A211" s="19">
         <v>222250000</v>
       </c>
@@ -18085,7 +18092,7 @@
       <c r="H211" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I211" s="19" t="s">
+      <c r="I211" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K211" s="19" t="s">
@@ -18119,7 +18126,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="212" s="19" customFormat="1" spans="1:21">
+    <row r="212" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A212" s="19">
         <v>222250001</v>
       </c>
@@ -18144,7 +18151,7 @@
       <c r="H212" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I212" s="19" t="s">
+      <c r="I212" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K212" s="19" t="s">
@@ -18178,7 +18185,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="213" s="19" customFormat="1" spans="1:21">
+    <row r="213" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A213" s="19">
         <v>222250002</v>
       </c>
@@ -18203,7 +18210,7 @@
       <c r="H213" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I213" s="19" t="s">
+      <c r="I213" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K213" s="19" t="s">
@@ -18237,7 +18244,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="214" s="19" customFormat="1" spans="1:21">
+    <row r="214" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A214" s="19">
         <v>222250003</v>
       </c>
@@ -18262,7 +18269,7 @@
       <c r="H214" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I214" s="19" t="s">
+      <c r="I214" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K214" s="19" t="s">
@@ -18296,7 +18303,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="215" s="19" customFormat="1" spans="1:21">
+    <row r="215" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A215" s="19">
         <v>222260000</v>
       </c>
@@ -18321,7 +18328,7 @@
       <c r="H215" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I215" s="19" t="s">
+      <c r="I215" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K215" s="19" t="s">
@@ -18355,7 +18362,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="216" s="19" customFormat="1" spans="1:21">
+    <row r="216" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A216" s="19">
         <v>222260001</v>
       </c>
@@ -18380,7 +18387,7 @@
       <c r="H216" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I216" s="19" t="s">
+      <c r="I216" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K216" s="19" t="s">
@@ -18414,7 +18421,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="217" s="19" customFormat="1" spans="1:21">
+    <row r="217" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A217" s="19">
         <v>222260002</v>
       </c>
@@ -18439,7 +18446,7 @@
       <c r="H217" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I217" s="19" t="s">
+      <c r="I217" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K217" s="19" t="s">
@@ -18473,7 +18480,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="218" s="19" customFormat="1" spans="1:21">
+    <row r="218" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A218" s="19">
         <v>222270000</v>
       </c>
@@ -18498,7 +18505,7 @@
       <c r="H218" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I218" s="19" t="s">
+      <c r="I218" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K218" s="19" t="s">
@@ -18532,7 +18539,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="219" s="19" customFormat="1" spans="1:21">
+    <row r="219" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A219" s="19">
         <v>222270001</v>
       </c>
@@ -18557,7 +18564,7 @@
       <c r="H219" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I219" s="19" t="s">
+      <c r="I219" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J219" s="19">
@@ -18594,7 +18601,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="220" s="19" customFormat="1" spans="1:21">
+    <row r="220" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A220" s="19">
         <v>222270002</v>
       </c>
@@ -18619,7 +18626,7 @@
       <c r="H220" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I220" s="19" t="s">
+      <c r="I220" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K220" s="19" t="s">
@@ -18653,7 +18660,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="221" s="19" customFormat="1" spans="1:21">
+    <row r="221" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A221" s="19">
         <v>222270003</v>
       </c>
@@ -18678,7 +18685,7 @@
       <c r="H221" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I221" s="19" t="s">
+      <c r="I221" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K221" s="19" t="s">
@@ -18712,7 +18719,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="222" s="19" customFormat="1" spans="1:21">
+    <row r="222" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A222" s="19">
         <v>222270004</v>
       </c>
@@ -18737,7 +18744,7 @@
       <c r="H222" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I222" s="19" t="s">
+      <c r="I222" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K222" s="19" t="s">
@@ -18771,7 +18778,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="223" s="19" customFormat="1" spans="1:21">
+    <row r="223" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A223" s="19">
         <v>222270005</v>
       </c>
@@ -18796,7 +18803,7 @@
       <c r="H223" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I223" s="19" t="s">
+      <c r="I223" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K223" s="19" t="s">
@@ -18830,7 +18837,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="224" s="19" customFormat="1" spans="1:21">
+    <row r="224" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A224" s="19">
         <v>222270006</v>
       </c>
@@ -18855,7 +18862,7 @@
       <c r="H224" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I224" s="19" t="s">
+      <c r="I224" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K224" s="19" t="s">
@@ -18889,7 +18896,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="225" s="19" customFormat="1" spans="1:21">
+    <row r="225" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A225" s="19">
         <v>222270007</v>
       </c>
@@ -18914,7 +18921,7 @@
       <c r="H225" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I225" s="19" t="s">
+      <c r="I225" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J225" s="19">
@@ -18951,7 +18958,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="226" s="19" customFormat="1" spans="1:21">
+    <row r="226" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A226" s="19">
         <v>222270008</v>
       </c>
@@ -18976,7 +18983,7 @@
       <c r="H226" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I226" s="19" t="s">
+      <c r="I226" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K226" s="19" t="s">
@@ -19573,7 +19580,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="237" s="16" customFormat="1" spans="1:21">
+    <row r="237" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A237" s="16">
         <v>412030000</v>
       </c>
@@ -19595,7 +19602,7 @@
       <c r="H237" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I237" s="16" t="s">
+      <c r="I237" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K237" s="16" t="s">
@@ -20135,7 +20142,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="247" s="16" customFormat="1" spans="1:21">
+    <row r="247" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A247" s="16">
         <v>412050000</v>
       </c>
@@ -20157,7 +20164,7 @@
       <c r="H247" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I247" s="16" t="s">
+      <c r="I247" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K247" s="16" t="s">
@@ -20191,7 +20198,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="248" s="16" customFormat="1" spans="1:21">
+    <row r="248" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A248" s="16">
         <v>412050001</v>
       </c>
@@ -20213,7 +20220,7 @@
       <c r="H248" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I248" s="16" t="s">
+      <c r="I248" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K248" s="16" t="s">
@@ -20247,7 +20254,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="249" s="16" customFormat="1" spans="1:21">
+    <row r="249" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A249" s="16">
         <v>412050002</v>
       </c>
@@ -20269,7 +20276,7 @@
       <c r="H249" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I249" s="16" t="s">
+      <c r="I249" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K249" s="16" t="s">
@@ -20303,7 +20310,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="250" s="16" customFormat="1" spans="1:21">
+    <row r="250" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A250" s="16">
         <v>412050003</v>
       </c>
@@ -20325,7 +20332,7 @@
       <c r="H250" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I250" s="16" t="s">
+      <c r="I250" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K250" s="1" t="s">
@@ -20359,7 +20366,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="251" s="16" customFormat="1" spans="1:21">
+    <row r="251" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A251" s="16">
         <v>412060000</v>
       </c>
@@ -20381,7 +20388,7 @@
       <c r="H251" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I251" s="16" t="s">
+      <c r="I251" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K251" s="16" t="s">
@@ -20415,7 +20422,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="252" s="16" customFormat="1" spans="1:21">
+    <row r="252" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A252" s="16">
         <v>412060001</v>
       </c>
@@ -20437,7 +20444,7 @@
       <c r="H252" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I252" s="16" t="s">
+      <c r="I252" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K252" s="16" t="s">
@@ -20471,7 +20478,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="253" s="16" customFormat="1" spans="1:21">
+    <row r="253" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A253" s="16">
         <v>412060002</v>
       </c>
@@ -20493,7 +20500,7 @@
       <c r="H253" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I253" s="16" t="s">
+      <c r="I253" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K253" s="16" t="s">
@@ -20527,7 +20534,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="254" s="16" customFormat="1" spans="1:21">
+    <row r="254" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A254" s="16">
         <v>412070000</v>
       </c>
@@ -20549,7 +20556,7 @@
       <c r="H254" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I254" s="16" t="s">
+      <c r="I254" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K254" s="16" t="s">
@@ -20583,7 +20590,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="255" s="16" customFormat="1" spans="1:21">
+    <row r="255" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A255" s="16">
         <v>412070001</v>
       </c>
@@ -20605,7 +20612,7 @@
       <c r="H255" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I255" s="16" t="s">
+      <c r="I255" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J255" s="16">
@@ -20642,7 +20649,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="256" s="16" customFormat="1" spans="1:21">
+    <row r="256" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A256" s="16">
         <v>412070002</v>
       </c>
@@ -20664,7 +20671,7 @@
       <c r="H256" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I256" s="16" t="s">
+      <c r="I256" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K256" s="16" t="s">
@@ -20698,7 +20705,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="257" s="16" customFormat="1" spans="1:21">
+    <row r="257" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A257" s="16">
         <v>412070003</v>
       </c>
@@ -20720,7 +20727,7 @@
       <c r="H257" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I257" s="16" t="s">
+      <c r="I257" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K257" s="16" t="s">
@@ -20754,7 +20761,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="258" s="16" customFormat="1" spans="1:21">
+    <row r="258" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A258" s="16">
         <v>412070004</v>
       </c>
@@ -20776,7 +20783,7 @@
       <c r="H258" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I258" s="16" t="s">
+      <c r="I258" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K258" s="16" t="s">
@@ -20810,7 +20817,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="259" s="16" customFormat="1" spans="1:21">
+    <row r="259" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A259" s="16">
         <v>412070005</v>
       </c>
@@ -20832,7 +20839,7 @@
       <c r="H259" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I259" s="16" t="s">
+      <c r="I259" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K259" s="16" t="s">
@@ -20866,7 +20873,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="260" s="16" customFormat="1" spans="1:21">
+    <row r="260" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A260" s="16">
         <v>412070006</v>
       </c>
@@ -20888,7 +20895,7 @@
       <c r="H260" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I260" s="16" t="s">
+      <c r="I260" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K260" s="16" t="s">
@@ -20922,7 +20929,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="261" s="16" customFormat="1" spans="1:21">
+    <row r="261" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A261" s="16">
         <v>412070007</v>
       </c>
@@ -20944,7 +20951,7 @@
       <c r="H261" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I261" s="16" t="s">
+      <c r="I261" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J261" s="16">
@@ -20981,7 +20988,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="262" s="16" customFormat="1" spans="1:21">
+    <row r="262" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A262" s="16">
         <v>412070008</v>
       </c>
@@ -21003,7 +21010,7 @@
       <c r="H262" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I262" s="16" t="s">
+      <c r="I262" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K262" s="1" t="s">
@@ -21584,7 +21591,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="272" s="16" customFormat="1" spans="1:21">
+    <row r="272" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A272" s="2">
         <v>412230000</v>
       </c>
@@ -21609,7 +21616,7 @@
       <c r="H272" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I272" s="2" t="s">
+      <c r="I272" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J272" s="2"/>
@@ -22176,7 +22183,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="282" s="16" customFormat="1" spans="1:21">
+    <row r="282" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A282" s="16">
         <v>412250000</v>
       </c>
@@ -22201,7 +22208,7 @@
       <c r="H282" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I282" s="16" t="s">
+      <c r="I282" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K282" s="16" t="s">
@@ -22235,7 +22242,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="283" s="16" customFormat="1" spans="1:21">
+    <row r="283" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A283" s="16">
         <v>412250001</v>
       </c>
@@ -22260,7 +22267,7 @@
       <c r="H283" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I283" s="16" t="s">
+      <c r="I283" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K283" s="16" t="s">
@@ -22294,7 +22301,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="284" s="16" customFormat="1" spans="1:21">
+    <row r="284" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A284" s="16">
         <v>412250002</v>
       </c>
@@ -22319,7 +22326,7 @@
       <c r="H284" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I284" s="16" t="s">
+      <c r="I284" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K284" s="16" t="s">
@@ -22350,7 +22357,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="285" s="16" customFormat="1" spans="1:21">
+    <row r="285" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A285" s="16">
         <v>412250003</v>
       </c>
@@ -22375,7 +22382,7 @@
       <c r="H285" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I285" s="16" t="s">
+      <c r="I285" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K285" s="2" t="s">
@@ -22409,7 +22416,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="286" s="16" customFormat="1" spans="1:21">
+    <row r="286" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A286" s="16">
         <v>412260000</v>
       </c>
@@ -22434,7 +22441,7 @@
       <c r="H286" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I286" s="16" t="s">
+      <c r="I286" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K286" s="16" t="s">
@@ -22468,7 +22475,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="287" s="16" customFormat="1" spans="1:21">
+    <row r="287" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A287" s="16">
         <v>412260001</v>
       </c>
@@ -22493,7 +22500,7 @@
       <c r="H287" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I287" s="16" t="s">
+      <c r="I287" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K287" s="16" t="s">
@@ -22527,7 +22534,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="288" s="16" customFormat="1" spans="1:21">
+    <row r="288" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A288" s="16">
         <v>412260002</v>
       </c>
@@ -22552,7 +22559,7 @@
       <c r="H288" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I288" s="16" t="s">
+      <c r="I288" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K288" s="16" t="s">
@@ -22586,7 +22593,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="289" s="16" customFormat="1" spans="1:21">
+    <row r="289" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A289" s="16">
         <v>412270000</v>
       </c>
@@ -22611,7 +22618,7 @@
       <c r="H289" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I289" s="16" t="s">
+      <c r="I289" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K289" s="16" t="s">
@@ -22645,7 +22652,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="290" s="16" customFormat="1" spans="1:21">
+    <row r="290" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A290" s="16">
         <v>412270001</v>
       </c>
@@ -22670,7 +22677,7 @@
       <c r="H290" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I290" s="16" t="s">
+      <c r="I290" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J290" s="2">
@@ -22708,7 +22715,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="291" s="16" customFormat="1" spans="1:21">
+    <row r="291" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A291" s="16">
         <v>412270002</v>
       </c>
@@ -22733,7 +22740,7 @@
       <c r="H291" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I291" s="16" t="s">
+      <c r="I291" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K291" s="16" t="s">
@@ -22767,7 +22774,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="292" s="16" customFormat="1" spans="1:21">
+    <row r="292" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A292" s="16">
         <v>412270003</v>
       </c>
@@ -22792,7 +22799,7 @@
       <c r="H292" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I292" s="16" t="s">
+      <c r="I292" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K292" s="16" t="s">
@@ -22826,7 +22833,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="293" s="16" customFormat="1" spans="1:21">
+    <row r="293" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A293" s="16">
         <v>412270004</v>
       </c>
@@ -22851,7 +22858,7 @@
       <c r="H293" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I293" s="16" t="s">
+      <c r="I293" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K293" s="16" t="s">
@@ -22885,7 +22892,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="294" s="16" customFormat="1" spans="1:21">
+    <row r="294" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A294" s="16">
         <v>412270005</v>
       </c>
@@ -22910,7 +22917,7 @@
       <c r="H294" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I294" s="16" t="s">
+      <c r="I294" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K294" s="16" t="s">
@@ -22944,7 +22951,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="295" s="16" customFormat="1" spans="1:21">
+    <row r="295" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A295" s="16">
         <v>412270006</v>
       </c>
@@ -22969,7 +22976,7 @@
       <c r="H295" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I295" s="16" t="s">
+      <c r="I295" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K295" s="16" t="s">
@@ -23003,7 +23010,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="296" s="16" customFormat="1" spans="1:21">
+    <row r="296" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A296" s="16">
         <v>412270007</v>
       </c>
@@ -23028,7 +23035,7 @@
       <c r="H296" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I296" s="16" t="s">
+      <c r="I296" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J296" s="2">
@@ -23066,7 +23073,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="297" s="16" customFormat="1" spans="1:21">
+    <row r="297" s="16" customFormat="1" ht="15" spans="1:21">
       <c r="A297" s="16">
         <v>412270008</v>
       </c>
@@ -23091,7 +23098,7 @@
       <c r="H297" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="I297" s="16" t="s">
+      <c r="I297" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K297" s="16" t="s">
@@ -23685,7 +23692,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="308" s="19" customFormat="1" spans="1:21">
+    <row r="308" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A308" s="19">
         <v>422030000</v>
       </c>
@@ -23707,7 +23714,7 @@
       <c r="H308" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I308" s="19" t="s">
+      <c r="I308" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K308" s="19" t="s">
@@ -24247,7 +24254,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="318" s="19" customFormat="1" spans="1:21">
+    <row r="318" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A318" s="19">
         <v>422050000</v>
       </c>
@@ -24269,7 +24276,7 @@
       <c r="H318" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I318" s="19" t="s">
+      <c r="I318" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K318" s="19" t="s">
@@ -24303,7 +24310,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="319" s="19" customFormat="1" spans="1:21">
+    <row r="319" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A319" s="19">
         <v>422050001</v>
       </c>
@@ -24325,7 +24332,7 @@
       <c r="H319" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I319" s="19" t="s">
+      <c r="I319" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K319" s="19" t="s">
@@ -24359,7 +24366,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="320" s="19" customFormat="1" spans="1:21">
+    <row r="320" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A320" s="19">
         <v>422050002</v>
       </c>
@@ -24381,7 +24388,7 @@
       <c r="H320" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I320" s="19" t="s">
+      <c r="I320" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K320" s="19" t="s">
@@ -24415,7 +24422,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="321" s="19" customFormat="1" spans="1:21">
+    <row r="321" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A321" s="19">
         <v>422050003</v>
       </c>
@@ -24437,7 +24444,7 @@
       <c r="H321" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I321" s="19" t="s">
+      <c r="I321" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K321" s="19" t="s">
@@ -24471,7 +24478,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="322" s="19" customFormat="1" spans="1:21">
+    <row r="322" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A322" s="19">
         <v>422060000</v>
       </c>
@@ -24493,7 +24500,7 @@
       <c r="H322" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I322" s="19" t="s">
+      <c r="I322" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K322" s="19" t="s">
@@ -24527,7 +24534,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="323" s="19" customFormat="1" spans="1:21">
+    <row r="323" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A323" s="19">
         <v>422060001</v>
       </c>
@@ -24549,7 +24556,7 @@
       <c r="H323" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I323" s="19" t="s">
+      <c r="I323" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K323" s="19" t="s">
@@ -24583,7 +24590,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="324" s="19" customFormat="1" spans="1:21">
+    <row r="324" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A324" s="19">
         <v>422060002</v>
       </c>
@@ -24605,7 +24612,7 @@
       <c r="H324" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I324" s="19" t="s">
+      <c r="I324" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K324" s="19" t="s">
@@ -24639,7 +24646,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="325" s="19" customFormat="1" spans="1:21">
+    <row r="325" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A325" s="19">
         <v>422070000</v>
       </c>
@@ -24661,7 +24668,7 @@
       <c r="H325" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I325" s="19" t="s">
+      <c r="I325" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K325" s="19" t="s">
@@ -24695,7 +24702,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="326" s="19" customFormat="1" spans="1:21">
+    <row r="326" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A326" s="19">
         <v>422070001</v>
       </c>
@@ -24717,7 +24724,7 @@
       <c r="H326" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I326" s="19" t="s">
+      <c r="I326" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J326" s="19">
@@ -24754,7 +24761,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="327" s="19" customFormat="1" spans="1:21">
+    <row r="327" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A327" s="19">
         <v>422070002</v>
       </c>
@@ -24776,7 +24783,7 @@
       <c r="H327" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I327" s="19" t="s">
+      <c r="I327" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K327" s="19" t="s">
@@ -24810,7 +24817,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="328" s="19" customFormat="1" spans="1:21">
+    <row r="328" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A328" s="19">
         <v>422070003</v>
       </c>
@@ -24832,7 +24839,7 @@
       <c r="H328" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I328" s="19" t="s">
+      <c r="I328" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K328" s="19" t="s">
@@ -24866,7 +24873,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="329" s="19" customFormat="1" spans="1:21">
+    <row r="329" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A329" s="19">
         <v>422070004</v>
       </c>
@@ -24888,7 +24895,7 @@
       <c r="H329" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I329" s="19" t="s">
+      <c r="I329" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K329" s="19" t="s">
@@ -24922,7 +24929,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="330" s="19" customFormat="1" spans="1:21">
+    <row r="330" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A330" s="19">
         <v>422070005</v>
       </c>
@@ -24944,7 +24951,7 @@
       <c r="H330" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I330" s="19" t="s">
+      <c r="I330" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K330" s="19" t="s">
@@ -24978,7 +24985,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="331" s="19" customFormat="1" spans="1:21">
+    <row r="331" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A331" s="19">
         <v>422070006</v>
       </c>
@@ -25000,7 +25007,7 @@
       <c r="H331" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I331" s="19" t="s">
+      <c r="I331" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K331" s="19" t="s">
@@ -25034,7 +25041,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="332" s="19" customFormat="1" spans="1:21">
+    <row r="332" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A332" s="19">
         <v>422070007</v>
       </c>
@@ -25056,7 +25063,7 @@
       <c r="H332" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I332" s="19" t="s">
+      <c r="I332" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J332" s="19">
@@ -25093,7 +25100,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="333" s="19" customFormat="1" spans="1:21">
+    <row r="333" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A333" s="19">
         <v>422070008</v>
       </c>
@@ -25115,7 +25122,7 @@
       <c r="H333" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I333" s="19" t="s">
+      <c r="I333" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K333" s="19" t="s">
@@ -25680,7 +25687,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="343" s="19" customFormat="1" spans="1:21">
+    <row r="343" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A343" s="19">
         <v>422230000</v>
       </c>
@@ -25705,7 +25712,7 @@
       <c r="H343" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I343" s="19" t="s">
+      <c r="I343" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K343" s="19" t="s">
@@ -26258,7 +26265,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="353" s="19" customFormat="1" spans="1:21">
+    <row r="353" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A353" s="19">
         <v>422250000</v>
       </c>
@@ -26283,7 +26290,7 @@
       <c r="H353" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I353" s="19" t="s">
+      <c r="I353" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K353" s="19" t="s">
@@ -26317,7 +26324,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="354" s="19" customFormat="1" spans="1:21">
+    <row r="354" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A354" s="19">
         <v>422250001</v>
       </c>
@@ -26342,7 +26349,7 @@
       <c r="H354" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I354" s="19" t="s">
+      <c r="I354" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K354" s="19" t="s">
@@ -26376,7 +26383,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="355" s="19" customFormat="1" spans="1:21">
+    <row r="355" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A355" s="19">
         <v>422250002</v>
       </c>
@@ -26401,7 +26408,7 @@
       <c r="H355" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I355" s="19" t="s">
+      <c r="I355" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K355" s="19" t="s">
@@ -26435,7 +26442,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="356" s="19" customFormat="1" spans="1:21">
+    <row r="356" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A356" s="19">
         <v>422250003</v>
       </c>
@@ -26460,7 +26467,7 @@
       <c r="H356" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I356" s="19" t="s">
+      <c r="I356" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K356" s="19" t="s">
@@ -26494,7 +26501,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="357" s="19" customFormat="1" spans="1:21">
+    <row r="357" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A357" s="19">
         <v>422260000</v>
       </c>
@@ -26519,7 +26526,7 @@
       <c r="H357" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I357" s="19" t="s">
+      <c r="I357" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K357" s="19" t="s">
@@ -26553,7 +26560,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="358" s="19" customFormat="1" spans="1:21">
+    <row r="358" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A358" s="19">
         <v>422260001</v>
       </c>
@@ -26578,7 +26585,7 @@
       <c r="H358" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I358" s="19" t="s">
+      <c r="I358" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K358" s="19" t="s">
@@ -26612,7 +26619,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="359" s="19" customFormat="1" spans="1:21">
+    <row r="359" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A359" s="19">
         <v>422260002</v>
       </c>
@@ -26637,7 +26644,7 @@
       <c r="H359" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I359" s="19" t="s">
+      <c r="I359" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K359" s="19" t="s">
@@ -26671,7 +26678,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="360" s="19" customFormat="1" spans="1:21">
+    <row r="360" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A360" s="19">
         <v>422270000</v>
       </c>
@@ -26696,7 +26703,7 @@
       <c r="H360" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I360" s="19" t="s">
+      <c r="I360" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K360" s="19" t="s">
@@ -26730,7 +26737,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="361" s="19" customFormat="1" spans="1:21">
+    <row r="361" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A361" s="19">
         <v>422270001</v>
       </c>
@@ -26755,7 +26762,7 @@
       <c r="H361" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I361" s="19" t="s">
+      <c r="I361" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J361" s="19">
@@ -26792,7 +26799,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="362" s="19" customFormat="1" spans="1:21">
+    <row r="362" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A362" s="19">
         <v>422270002</v>
       </c>
@@ -26817,7 +26824,7 @@
       <c r="H362" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I362" s="19" t="s">
+      <c r="I362" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K362" s="19" t="s">
@@ -26851,7 +26858,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="363" s="19" customFormat="1" spans="1:21">
+    <row r="363" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A363" s="19">
         <v>422270003</v>
       </c>
@@ -26876,7 +26883,7 @@
       <c r="H363" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I363" s="19" t="s">
+      <c r="I363" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K363" s="19" t="s">
@@ -26910,7 +26917,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="364" s="19" customFormat="1" spans="1:21">
+    <row r="364" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A364" s="19">
         <v>422270004</v>
       </c>
@@ -26935,7 +26942,7 @@
       <c r="H364" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I364" s="19" t="s">
+      <c r="I364" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K364" s="19" t="s">
@@ -26969,7 +26976,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="365" s="19" customFormat="1" spans="1:21">
+    <row r="365" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A365" s="19">
         <v>422270005</v>
       </c>
@@ -26994,7 +27001,7 @@
       <c r="H365" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I365" s="19" t="s">
+      <c r="I365" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K365" s="19" t="s">
@@ -27028,7 +27035,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="366" s="19" customFormat="1" spans="1:21">
+    <row r="366" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A366" s="19">
         <v>422270006</v>
       </c>
@@ -27053,7 +27060,7 @@
       <c r="H366" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I366" s="19" t="s">
+      <c r="I366" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K366" s="19" t="s">
@@ -27087,7 +27094,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="367" s="19" customFormat="1" spans="1:21">
+    <row r="367" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A367" s="19">
         <v>422270007</v>
       </c>
@@ -27112,7 +27119,7 @@
       <c r="H367" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I367" s="19" t="s">
+      <c r="I367" s="24" t="s">
         <v>76</v>
       </c>
       <c r="J367" s="19">
@@ -27149,7 +27156,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="368" s="19" customFormat="1" spans="1:21">
+    <row r="368" s="19" customFormat="1" ht="15" spans="1:21">
       <c r="A368" s="19">
         <v>422270008</v>
       </c>
@@ -27174,7 +27181,7 @@
       <c r="H368" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I368" s="19" t="s">
+      <c r="I368" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K368" s="19" t="s">
@@ -27398,7 +27405,7 @@
       <c r="O375" s="16">
         <v>0</v>
       </c>
-      <c r="P375" s="24" t="s">
+      <c r="P375" s="25" t="s">
         <v>359</v>
       </c>
     </row>
@@ -27612,7 +27619,7 @@
       <c r="O383" s="20">
         <v>0</v>
       </c>
-      <c r="P383" s="25" t="s">
+      <c r="P383" s="26" t="s">
         <v>378</v>
       </c>
     </row>
@@ -27632,7 +27639,7 @@
       <c r="G384" s="21">
         <v>2</v>
       </c>
-      <c r="K384" s="26"/>
+      <c r="K384" s="27"/>
       <c r="M384" s="21">
         <v>1012000</v>
       </c>
@@ -27659,7 +27666,7 @@
       <c r="G385" s="21">
         <v>2</v>
       </c>
-      <c r="K385" s="26"/>
+      <c r="K385" s="27"/>
       <c r="M385" s="21">
         <v>1200001</v>
       </c>
@@ -27686,7 +27693,7 @@
       <c r="G386" s="21">
         <v>2</v>
       </c>
-      <c r="K386" s="26"/>
+      <c r="K386" s="27"/>
       <c r="M386" s="21">
         <v>1200002</v>
       </c>
@@ -27713,7 +27720,7 @@
       <c r="G387" s="21">
         <v>2</v>
       </c>
-      <c r="K387" s="26"/>
+      <c r="K387" s="27"/>
       <c r="M387" s="21">
         <v>1200003</v>
       </c>
@@ -27740,7 +27747,7 @@
       <c r="G388" s="21">
         <v>2</v>
       </c>
-      <c r="K388" s="26"/>
+      <c r="K388" s="27"/>
       <c r="M388" s="21">
         <v>1200004</v>
       </c>
@@ -27767,7 +27774,7 @@
       <c r="G389" s="21">
         <v>2</v>
       </c>
-      <c r="K389" s="26"/>
+      <c r="K389" s="27"/>
       <c r="M389" s="21">
         <v>1200006</v>
       </c>
@@ -27794,7 +27801,7 @@
       <c r="G390" s="21">
         <v>2</v>
       </c>
-      <c r="K390" s="26"/>
+      <c r="K390" s="27"/>
       <c r="M390" s="21">
         <v>1200013</v>
       </c>
@@ -27821,7 +27828,7 @@
       <c r="G391" s="21">
         <v>2</v>
       </c>
-      <c r="K391" s="26"/>
+      <c r="K391" s="27"/>
       <c r="M391" s="21">
         <v>1200014</v>
       </c>
@@ -27848,7 +27855,7 @@
       <c r="G392" s="21">
         <v>2</v>
       </c>
-      <c r="K392" s="26"/>
+      <c r="K392" s="27"/>
       <c r="M392" s="21">
         <v>1200015</v>
       </c>
@@ -27875,7 +27882,7 @@
       <c r="G393" s="21">
         <v>2</v>
       </c>
-      <c r="K393" s="26"/>
+      <c r="K393" s="27"/>
       <c r="M393" s="21">
         <v>1200017</v>
       </c>
@@ -29058,7 +29065,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="437" s="22" customFormat="1" spans="1:17">
+    <row r="437" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A437" s="22">
         <v>520302001</v>
       </c>
@@ -29074,7 +29081,7 @@
       <c r="G437" s="22">
         <v>3</v>
       </c>
-      <c r="I437" s="22" t="s">
+      <c r="I437" s="24" t="s">
         <v>76</v>
       </c>
       <c r="M437" s="22">
@@ -29087,7 +29094,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="438" s="22" customFormat="1" spans="1:17">
+    <row r="438" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A438" s="22">
         <v>520302002</v>
       </c>
@@ -29103,7 +29110,7 @@
       <c r="G438" s="22">
         <v>3</v>
       </c>
-      <c r="I438" s="22" t="s">
+      <c r="I438" s="24" t="s">
         <v>76</v>
       </c>
       <c r="M438" s="22">
@@ -29119,7 +29126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="439" s="22" customFormat="1" spans="1:17">
+    <row r="439" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A439" s="22">
         <v>520302003</v>
       </c>
@@ -29135,7 +29142,7 @@
       <c r="G439" s="22">
         <v>3</v>
       </c>
-      <c r="I439" s="22" t="s">
+      <c r="I439" s="24" t="s">
         <v>76</v>
       </c>
       <c r="M439" s="22">
@@ -29148,7 +29155,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="440" s="22" customFormat="1" spans="1:17">
+    <row r="440" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A440" s="22">
         <v>520302004</v>
       </c>
@@ -29164,7 +29171,7 @@
       <c r="G440" s="22">
         <v>3</v>
       </c>
-      <c r="I440" s="22" t="s">
+      <c r="I440" s="24" t="s">
         <v>76</v>
       </c>
       <c r="M440" s="22">
@@ -29177,7 +29184,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="441" s="22" customFormat="1" spans="1:17">
+    <row r="441" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A441" s="22">
         <v>520302005</v>
       </c>
@@ -29193,7 +29200,7 @@
       <c r="G441" s="22">
         <v>3</v>
       </c>
-      <c r="I441" s="22" t="s">
+      <c r="I441" s="24" t="s">
         <v>76</v>
       </c>
       <c r="M441" s="22">
@@ -29206,7 +29213,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="442" s="22" customFormat="1" spans="1:17">
+    <row r="442" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A442" s="22">
         <v>520303001</v>
       </c>
@@ -29222,7 +29229,7 @@
       <c r="G442" s="22">
         <v>3</v>
       </c>
-      <c r="I442" s="22" t="s">
+      <c r="I442" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K442" s="22" t="s">
@@ -29238,7 +29245,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="443" s="22" customFormat="1" spans="1:17">
+    <row r="443" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A443" s="22">
         <v>520303002</v>
       </c>
@@ -29254,7 +29261,7 @@
       <c r="G443" s="22">
         <v>3</v>
       </c>
-      <c r="I443" s="22" t="s">
+      <c r="I443" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K443" s="22" t="s">
@@ -29270,7 +29277,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="444" s="22" customFormat="1" spans="1:17">
+    <row r="444" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A444" s="22">
         <v>520303003</v>
       </c>
@@ -29286,7 +29293,7 @@
       <c r="G444" s="22">
         <v>3</v>
       </c>
-      <c r="I444" s="22" t="s">
+      <c r="I444" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K444" s="22" t="s">
@@ -29302,7 +29309,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="445" s="22" customFormat="1" spans="1:17">
+    <row r="445" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A445" s="22">
         <v>520303004</v>
       </c>
@@ -29318,7 +29325,7 @@
       <c r="G445" s="22">
         <v>3</v>
       </c>
-      <c r="I445" s="22" t="s">
+      <c r="I445" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K445" s="22" t="s">
@@ -29334,7 +29341,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="446" s="22" customFormat="1" spans="1:17">
+    <row r="446" s="22" customFormat="1" ht="15" spans="1:17">
       <c r="A446" s="22">
         <v>520303005</v>
       </c>
@@ -29350,7 +29357,7 @@
       <c r="G446" s="22">
         <v>3</v>
       </c>
-      <c r="I446" s="22" t="s">
+      <c r="I446" s="24" t="s">
         <v>76</v>
       </c>
       <c r="K446" s="22" t="s">
@@ -29489,7 +29496,7 @@
       <c r="G451" s="16">
         <v>6</v>
       </c>
-      <c r="M451" s="27">
+      <c r="M451" s="28">
         <v>1016005</v>
       </c>
       <c r="O451" s="22" t="s">
@@ -29616,7 +29623,7 @@
       <c r="G456" s="16">
         <v>6</v>
       </c>
-      <c r="M456" s="28">
+      <c r="M456" s="29">
         <v>1016017</v>
       </c>
       <c r="O456" s="22" t="s">
@@ -29642,7 +29649,7 @@
       <c r="G457" s="16">
         <v>6</v>
       </c>
-      <c r="M457" s="28">
+      <c r="M457" s="29">
         <v>1016018</v>
       </c>
       <c r="O457" s="22" t="s">
@@ -29668,7 +29675,7 @@
       <c r="G458" s="16">
         <v>6</v>
       </c>
-      <c r="M458" s="28">
+      <c r="M458" s="29">
         <v>1016019</v>
       </c>
       <c r="O458" s="22" t="s">
@@ -29943,7 +29950,7 @@
       <c r="G468" s="16">
         <v>4</v>
       </c>
-      <c r="K468" s="26"/>
+      <c r="K468" s="27"/>
       <c r="M468" s="21">
         <v>1200002</v>
       </c>
@@ -29970,7 +29977,7 @@
       <c r="G469" s="16">
         <v>4</v>
       </c>
-      <c r="K469" s="26"/>
+      <c r="K469" s="27"/>
       <c r="M469" s="21">
         <v>1200003</v>
       </c>
@@ -29997,7 +30004,7 @@
       <c r="G470" s="16">
         <v>4</v>
       </c>
-      <c r="K470" s="26"/>
+      <c r="K470" s="27"/>
       <c r="M470" s="21">
         <v>1200004</v>
       </c>
@@ -30024,7 +30031,7 @@
       <c r="G471" s="16">
         <v>4</v>
       </c>
-      <c r="K471" s="26"/>
+      <c r="K471" s="27"/>
       <c r="M471" s="21">
         <v>1200006</v>
       </c>
@@ -30051,7 +30058,7 @@
       <c r="G472" s="16">
         <v>4</v>
       </c>
-      <c r="K472" s="26"/>
+      <c r="K472" s="27"/>
       <c r="M472" s="21">
         <v>1200013</v>
       </c>
@@ -30078,7 +30085,7 @@
       <c r="G473" s="16">
         <v>4</v>
       </c>
-      <c r="K473" s="26"/>
+      <c r="K473" s="27"/>
       <c r="M473" s="21">
         <v>1200014</v>
       </c>
@@ -30319,7 +30326,7 @@
       <c r="O482" s="21" t="s">
         <v>347</v>
       </c>
-      <c r="P482" s="29" t="s">
+      <c r="P482" s="30" t="s">
         <v>496</v>
       </c>
     </row>
@@ -30721,36 +30728,63 @@
     </row>
     <row r="492" s="16" customFormat="1" spans="1:21">
       <c r="A492" s="16">
-        <v>520500000</v>
+        <v>610070000</v>
       </c>
       <c r="B492" s="16" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="C492" s="16">
-        <v>5</v>
-      </c>
-      <c r="D492" s="16">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="D492" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="G492" s="16">
-        <v>5</v>
-      </c>
-      <c r="M492" s="16">
-        <v>1015000</v>
-      </c>
-      <c r="O492" s="16">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="H492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="K492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="O492" s="16" t="s">
+        <v>72</v>
       </c>
       <c r="P492" s="16" t="s">
-        <v>510</v>
+        <v>503</v>
+      </c>
+      <c r="Q492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="R492" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="S492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="T492" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="U492" s="16" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="493" s="16" customFormat="1" spans="1:21">
       <c r="A493" s="16">
-        <v>520500001</v>
+        <v>520500000</v>
       </c>
       <c r="B493" s="16" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C493" s="16">
         <v>5</v>
@@ -30762,7 +30796,7 @@
         <v>5</v>
       </c>
       <c r="M493" s="16">
-        <v>1014012</v>
+        <v>1015000</v>
       </c>
       <c r="O493" s="16">
         <v>0</v>
@@ -30773,10 +30807,10 @@
     </row>
     <row r="494" s="16" customFormat="1" spans="1:21">
       <c r="A494" s="16">
-        <v>520500002</v>
+        <v>520500001</v>
       </c>
       <c r="B494" s="16" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C494" s="16">
         <v>5</v>
@@ -30788,7 +30822,7 @@
         <v>5</v>
       </c>
       <c r="M494" s="16">
-        <v>1005001</v>
+        <v>1014012</v>
       </c>
       <c r="O494" s="16">
         <v>0</v>
@@ -30799,10 +30833,10 @@
     </row>
     <row r="495" s="16" customFormat="1" spans="1:21">
       <c r="A495" s="16">
-        <v>520500003</v>
+        <v>520500002</v>
       </c>
       <c r="B495" s="16" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C495" s="16">
         <v>5</v>
@@ -30813,8 +30847,8 @@
       <c r="G495" s="16">
         <v>5</v>
       </c>
-      <c r="M495" s="30">
-        <v>1014026</v>
+      <c r="M495" s="16">
+        <v>1005001</v>
       </c>
       <c r="O495" s="16">
         <v>0</v>
@@ -30825,10 +30859,10 @@
     </row>
     <row r="496" s="16" customFormat="1" spans="1:21">
       <c r="A496" s="16">
-        <v>520500004</v>
+        <v>520500003</v>
       </c>
       <c r="B496" s="16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C496" s="16">
         <v>5</v>
@@ -30839,8 +30873,8 @@
       <c r="G496" s="16">
         <v>5</v>
       </c>
-      <c r="M496" s="16">
-        <v>1014014</v>
+      <c r="M496" s="31">
+        <v>1014026</v>
       </c>
       <c r="O496" s="16">
         <v>0</v>
@@ -30851,10 +30885,10 @@
     </row>
     <row r="497" s="16" customFormat="1" spans="1:16">
       <c r="A497" s="16">
-        <v>520500005</v>
+        <v>520500004</v>
       </c>
       <c r="B497" s="16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C497" s="16">
         <v>5</v>
@@ -30866,7 +30900,7 @@
         <v>5</v>
       </c>
       <c r="M497" s="16">
-        <v>1005002</v>
+        <v>1014014</v>
       </c>
       <c r="O497" s="16">
         <v>0</v>
@@ -30875,172 +30909,198 @@
         <v>510</v>
       </c>
     </row>
+    <row r="498" s="16" customFormat="1" spans="1:16">
+      <c r="A498" s="16">
+        <v>520500005</v>
+      </c>
+      <c r="B498" s="16" t="s">
+        <v>515</v>
+      </c>
+      <c r="C498" s="16">
+        <v>5</v>
+      </c>
+      <c r="D498" s="16">
+        <v>2</v>
+      </c>
+      <c r="G498" s="16">
+        <v>5</v>
+      </c>
+      <c r="M498" s="16">
+        <v>1005002</v>
+      </c>
+      <c r="O498" s="16">
+        <v>0</v>
+      </c>
+      <c r="P498" s="16" t="s">
+        <v>510</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U498" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:V498" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="0" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="157"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="0" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A127">
+    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A128">
+    <cfRule type="duplicateValues" dxfId="0" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A129">
+    <cfRule type="duplicateValues" dxfId="0" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A130">
+    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A131">
     <cfRule type="duplicateValues" dxfId="0" priority="146"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A128">
-    <cfRule type="duplicateValues" dxfId="0" priority="145"/>
+  <conditionalFormatting sqref="A162">
+    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A129">
-    <cfRule type="duplicateValues" dxfId="0" priority="144"/>
+  <conditionalFormatting sqref="A269">
+    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A130">
-    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A131">
-    <cfRule type="duplicateValues" dxfId="0" priority="142"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A162">
+  <conditionalFormatting sqref="A270">
     <cfRule type="duplicateValues" dxfId="0" priority="116"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A269">
+  <conditionalFormatting sqref="A271">
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A272">
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A273">
     <cfRule type="duplicateValues" dxfId="0" priority="113"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A270">
+  <conditionalFormatting sqref="A304">
     <cfRule type="duplicateValues" dxfId="0" priority="112"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A271">
+  <conditionalFormatting sqref="K393">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A449">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M449">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M451">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M453">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M480">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M481">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A485">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M485">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A492">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A493">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A459:A461">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A462:A467">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A468:A473">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A474:A477">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A478:A484">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K385:K392">
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K468:K473">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M385:M401">
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M406:M421">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M437:M438">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M442:M443">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M468:M473">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M474:M477">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M478:M479">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M482:M484">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A4 A494:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="239"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A448 A450:A458 A486:A491 A494:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="111"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A272">
+  <conditionalFormatting sqref="A5:A16 A21:A126 A132:A161 A163:A226 A486:A491">
+    <cfRule type="duplicateValues" dxfId="0" priority="160"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A227:A268 A274:A303 A305:A368">
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A369:A448 A450:A458">
     <cfRule type="duplicateValues" dxfId="0" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A273">
-    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+  <conditionalFormatting sqref="K385:K388 K390">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A304">
-    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
+  <conditionalFormatting sqref="K389 K391:K392">
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K393">
-    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+  <conditionalFormatting sqref="M422:M436 M439:M441">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A449">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="M444:M446 M450 M452 M454:M458">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M449">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M451">
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M453">
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M480">
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M481">
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A485">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M485">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A492">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A498">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A459:A461">
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A462:A467">
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A468:A473">
+  <conditionalFormatting sqref="K468:K470 K472">
     <cfRule type="duplicateValues" dxfId="0" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A474:A477">
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A478:A484">
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K385:K392">
-    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K468:K473">
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M385:M401">
-    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M406:M421">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M437:M438">
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M442:M443">
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M468:M473">
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M474:M477">
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M478:M479">
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M482:M484">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A4 A493:A497 A499:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="235"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A448 A450:A458 A486:A491 A493:A497 A499:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A16 A21:A126 A132:A161 A163:A226 A486:A491">
-    <cfRule type="duplicateValues" dxfId="0" priority="156"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A227:A268 A274:A303 A305:A368">
-    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A369:A448 A450:A458">
-    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K385:K388 K390">
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K389 K391:K392">
-    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M422:M436 M439:M441">
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M444:M446 M450 M452 M454:M458">
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K468:K470 K472">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K471 K473">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="P482" r:id="rId1" display="SwordMan@huojianxi" tooltip="mailto:SwordMan@huojianxi"/>
